--- a/analysis/gear_testing_2026/data/2026_gear_testing_haul_log.xlsx
+++ b/analysis/gear_testing_2026/data/2026_gear_testing_haul_log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sean.rohan\Work\afsc\trawlmetrics\analysis\gear_testing_2026\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D922AFD-9504-4E12-8D44-17FDF8315C54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A208E355-B3F8-4114-842E-90D8636CBBA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{25452425-81FD-47B5-9EE2-CB06642CF5FF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{25452425-81FD-47B5-9EE2-CB06642CF5FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="28">
   <si>
     <t>Haul</t>
   </si>
@@ -124,6 +124,9 @@
   <si>
     <t>Second haulback</t>
   </si>
+  <si>
+    <t>Scope table</t>
+  </si>
 </sst>
 </file>
 
@@ -199,7 +202,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -210,7 +213,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -550,7 +555,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BF1202A3-421A-4DB2-8CEE-A066F1DE6A6E}">
-  <dimension ref="A1:S163"/>
+  <dimension ref="A1:S187"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="15.85546875" style="5" customWidth="1"/>
@@ -562,7 +567,8 @@
     <col min="10" max="10" width="17" style="7" customWidth="1"/>
     <col min="11" max="11" width="9.140625" style="4" customWidth="1"/>
     <col min="12" max="14" width="17.42578125" style="4" customWidth="1"/>
-    <col min="15" max="17" width="9.140625" customWidth="1"/>
+    <col min="15" max="15" width="14.28515625" customWidth="1"/>
+    <col min="16" max="17" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
@@ -8304,6 +8310,808 @@
         <v>1</v>
       </c>
     </row>
+    <row r="164" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A164" s="12">
+        <v>531</v>
+      </c>
+      <c r="B164" s="8">
+        <v>46241</v>
+      </c>
+      <c r="C164" s="9">
+        <v>0.36021990740740739</v>
+      </c>
+      <c r="D164" s="12">
+        <v>40</v>
+      </c>
+      <c r="E164" s="3"/>
+      <c r="F164" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G164" s="7">
+        <v>3.6</v>
+      </c>
+      <c r="H164" s="7">
+        <v>12.5</v>
+      </c>
+      <c r="I164" s="7">
+        <v>-2.2000000000000002</v>
+      </c>
+      <c r="J164" s="7">
+        <v>6.9</v>
+      </c>
+      <c r="K164" s="4">
+        <v>3.5</v>
+      </c>
+      <c r="L164" s="4">
+        <v>12.4</v>
+      </c>
+      <c r="M164" s="4">
+        <v>-3.6</v>
+      </c>
+      <c r="N164" s="4">
+        <v>-5.3</v>
+      </c>
+      <c r="P164" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q164" s="11">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="165" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A165" s="12">
+        <v>531</v>
+      </c>
+      <c r="B165" s="8">
+        <v>46241</v>
+      </c>
+      <c r="C165" s="9">
+        <v>0.36368055555555556</v>
+      </c>
+      <c r="D165" s="12">
+        <v>40</v>
+      </c>
+      <c r="E165" s="3"/>
+      <c r="F165" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="P165" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q165" s="11">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="166" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A166" s="12">
+        <v>531</v>
+      </c>
+      <c r="B166" s="8">
+        <v>46241</v>
+      </c>
+      <c r="C166" s="9">
+        <v>0.36525462962962962</v>
+      </c>
+      <c r="D166" s="12">
+        <v>50</v>
+      </c>
+      <c r="E166" s="3"/>
+      <c r="F166" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G166" s="7">
+        <v>2.9</v>
+      </c>
+      <c r="H166" s="7">
+        <v>15.9</v>
+      </c>
+      <c r="I166" s="7">
+        <v>-3.4</v>
+      </c>
+      <c r="J166" s="7">
+        <v>5</v>
+      </c>
+      <c r="K166" s="4">
+        <v>2.8</v>
+      </c>
+      <c r="L166" s="4">
+        <v>15.4</v>
+      </c>
+      <c r="M166" s="4">
+        <v>-4</v>
+      </c>
+      <c r="N166" s="4">
+        <v>-6.6</v>
+      </c>
+      <c r="P166" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q166" s="11">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="167" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A167" s="12">
+        <v>531</v>
+      </c>
+      <c r="B167" s="8">
+        <v>46241</v>
+      </c>
+      <c r="C167" s="9">
+        <v>0.36782407407407408</v>
+      </c>
+      <c r="D167" s="12">
+        <v>50</v>
+      </c>
+      <c r="E167" s="3"/>
+      <c r="F167" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="P167" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q167" s="11">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="168" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A168" s="12">
+        <v>531</v>
+      </c>
+      <c r="B168" s="8">
+        <v>46241</v>
+      </c>
+      <c r="C168" s="9">
+        <v>0.36953703703703705</v>
+      </c>
+      <c r="D168" s="12">
+        <v>60</v>
+      </c>
+      <c r="E168" s="3"/>
+      <c r="F168" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G168" s="7">
+        <v>2.8</v>
+      </c>
+      <c r="H168" s="7">
+        <v>21.2</v>
+      </c>
+      <c r="I168" s="7">
+        <v>-3.4</v>
+      </c>
+      <c r="J168" s="7">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="K168" s="4">
+        <v>2.8</v>
+      </c>
+      <c r="L168" s="4">
+        <v>19.600000000000001</v>
+      </c>
+      <c r="M168" s="4">
+        <v>-4.0999999999999996</v>
+      </c>
+      <c r="N168" s="4">
+        <v>-4.3</v>
+      </c>
+      <c r="P168" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q168" s="11">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="169" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A169" s="12">
+        <v>531</v>
+      </c>
+      <c r="B169" s="8">
+        <v>46241</v>
+      </c>
+      <c r="C169" s="9">
+        <v>0.37291666666666667</v>
+      </c>
+      <c r="D169" s="12">
+        <v>60</v>
+      </c>
+      <c r="E169" s="3"/>
+      <c r="F169" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="P169" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q169" s="11">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="170" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A170" s="12">
+        <v>531</v>
+      </c>
+      <c r="B170" s="8">
+        <v>46241</v>
+      </c>
+      <c r="C170" s="9">
+        <v>0.37415509259259261</v>
+      </c>
+      <c r="D170" s="12">
+        <v>70</v>
+      </c>
+      <c r="E170" s="3"/>
+      <c r="F170" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G170" s="7">
+        <v>2.8</v>
+      </c>
+      <c r="H170" s="7">
+        <v>23.9</v>
+      </c>
+      <c r="I170" s="7">
+        <v>-4.7</v>
+      </c>
+      <c r="J170" s="7">
+        <v>5.9</v>
+      </c>
+      <c r="K170" s="4">
+        <v>2.7</v>
+      </c>
+      <c r="L170" s="4">
+        <v>23.6</v>
+      </c>
+      <c r="M170" s="4">
+        <v>-5</v>
+      </c>
+      <c r="N170" s="4">
+        <v>-5.9</v>
+      </c>
+      <c r="P170" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q170" s="11">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="171" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A171" s="12">
+        <v>531</v>
+      </c>
+      <c r="B171" s="8">
+        <v>46241</v>
+      </c>
+      <c r="C171" s="9">
+        <v>0.37776620370370373</v>
+      </c>
+      <c r="D171" s="12">
+        <v>70</v>
+      </c>
+      <c r="E171" s="3"/>
+      <c r="F171" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="P171" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q171" s="11">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="172" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A172" s="12">
+        <v>531</v>
+      </c>
+      <c r="B172" s="8">
+        <v>46241</v>
+      </c>
+      <c r="C172" s="9">
+        <v>0.37921296296296297</v>
+      </c>
+      <c r="D172" s="12">
+        <v>80</v>
+      </c>
+      <c r="E172" s="3"/>
+      <c r="F172" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G172" s="7">
+        <v>2.7</v>
+      </c>
+      <c r="H172" s="7">
+        <v>24.4</v>
+      </c>
+      <c r="I172" s="7">
+        <v>-5.4</v>
+      </c>
+      <c r="J172" s="7">
+        <v>10.3</v>
+      </c>
+      <c r="K172" s="4">
+        <v>2.7</v>
+      </c>
+      <c r="L172" s="4">
+        <v>24.5</v>
+      </c>
+      <c r="M172" s="4">
+        <v>-6.1</v>
+      </c>
+      <c r="N172" s="4">
+        <v>-9.1999999999999993</v>
+      </c>
+      <c r="P172" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q172" s="11">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="173" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A173" s="12">
+        <v>531</v>
+      </c>
+      <c r="B173" s="8">
+        <v>46241</v>
+      </c>
+      <c r="C173" s="9">
+        <v>0.38237268518518519</v>
+      </c>
+      <c r="D173" s="12">
+        <v>80</v>
+      </c>
+      <c r="E173" s="3"/>
+      <c r="F173" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="P173" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q173" s="11">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="174" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A174" s="12">
+        <v>531</v>
+      </c>
+      <c r="B174" s="8">
+        <v>46241</v>
+      </c>
+      <c r="C174" s="6">
+        <v>0.3837962962962963</v>
+      </c>
+      <c r="D174" s="11">
+        <v>90</v>
+      </c>
+      <c r="F174" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G174" s="7">
+        <v>2.8</v>
+      </c>
+      <c r="H174" s="7">
+        <v>24.3</v>
+      </c>
+      <c r="I174" s="7">
+        <v>-7.8</v>
+      </c>
+      <c r="J174" s="7">
+        <v>17.8</v>
+      </c>
+      <c r="K174" s="4">
+        <v>2.7</v>
+      </c>
+      <c r="L174" s="4">
+        <v>24.4</v>
+      </c>
+      <c r="M174" s="4">
+        <v>-8.3000000000000007</v>
+      </c>
+      <c r="N174" s="4">
+        <v>-15.8</v>
+      </c>
+      <c r="P174" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q174" s="11">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="175" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A175" s="12">
+        <v>531</v>
+      </c>
+      <c r="B175" s="8">
+        <v>46241</v>
+      </c>
+      <c r="C175" s="6">
+        <v>0.38737268518518519</v>
+      </c>
+      <c r="D175" s="11">
+        <v>90</v>
+      </c>
+      <c r="F175" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="P175" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q175" s="11">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="176" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A176" s="11">
+        <v>532</v>
+      </c>
+      <c r="B176" s="8">
+        <v>46241</v>
+      </c>
+      <c r="C176" s="6">
+        <v>0.4274074074074074</v>
+      </c>
+      <c r="D176" s="11">
+        <v>70</v>
+      </c>
+      <c r="F176" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G176" s="7">
+        <v>2.7</v>
+      </c>
+      <c r="H176" s="7">
+        <v>23.8</v>
+      </c>
+      <c r="I176" s="7">
+        <v>-5.9</v>
+      </c>
+      <c r="J176" s="7">
+        <v>10.3</v>
+      </c>
+      <c r="K176" s="4">
+        <v>2.8</v>
+      </c>
+      <c r="L176" s="4">
+        <v>23.5</v>
+      </c>
+      <c r="M176" s="4">
+        <v>-5.8</v>
+      </c>
+      <c r="N176" s="4">
+        <v>-5</v>
+      </c>
+      <c r="P176" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q176" s="11">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A177" s="11">
+        <v>532</v>
+      </c>
+      <c r="B177" s="8">
+        <v>46241</v>
+      </c>
+      <c r="C177" s="6">
+        <v>0.43033564814814818</v>
+      </c>
+      <c r="D177" s="11">
+        <v>70</v>
+      </c>
+      <c r="F177" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="P177" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q177" s="11">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A178" s="11">
+        <v>532</v>
+      </c>
+      <c r="B178" s="8">
+        <v>46241</v>
+      </c>
+      <c r="C178" s="6">
+        <v>0.43177083333333333</v>
+      </c>
+      <c r="D178" s="11">
+        <v>80</v>
+      </c>
+      <c r="F178" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G178" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="H178" s="7">
+        <v>24.3</v>
+      </c>
+      <c r="I178" s="7">
+        <v>-6.6</v>
+      </c>
+      <c r="J178" s="7">
+        <v>14.7</v>
+      </c>
+      <c r="K178" s="4">
+        <v>2.5</v>
+      </c>
+      <c r="L178" s="4">
+        <v>24.3</v>
+      </c>
+      <c r="M178" s="4">
+        <v>-15.3</v>
+      </c>
+      <c r="N178" s="4">
+        <v>-12.5</v>
+      </c>
+      <c r="P178" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q178" s="11">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A179" s="11">
+        <v>532</v>
+      </c>
+      <c r="B179" s="8">
+        <v>46241</v>
+      </c>
+      <c r="C179" s="6">
+        <v>0.43511574074074072</v>
+      </c>
+      <c r="D179" s="11">
+        <v>80</v>
+      </c>
+      <c r="F179" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="P179" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q179" s="11">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A180" s="11">
+        <v>532</v>
+      </c>
+      <c r="B180" s="8">
+        <v>46241</v>
+      </c>
+      <c r="C180" s="6">
+        <v>0.43710648148148146</v>
+      </c>
+      <c r="D180" s="11">
+        <v>90</v>
+      </c>
+      <c r="F180" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G180" s="7">
+        <v>2.9</v>
+      </c>
+      <c r="H180" s="7">
+        <v>24.7</v>
+      </c>
+      <c r="I180" s="7">
+        <v>-7.2</v>
+      </c>
+      <c r="J180" s="7">
+        <v>17.7</v>
+      </c>
+      <c r="K180" s="4">
+        <v>2.9</v>
+      </c>
+      <c r="L180" s="4">
+        <v>24.8</v>
+      </c>
+      <c r="M180" s="4">
+        <v>-8</v>
+      </c>
+      <c r="N180" s="4">
+        <v>-12.4</v>
+      </c>
+    </row>
+    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A181" s="11">
+        <v>532</v>
+      </c>
+      <c r="B181" s="8">
+        <v>46241</v>
+      </c>
+      <c r="C181" s="6">
+        <v>0.43939814814814815</v>
+      </c>
+      <c r="D181" s="11">
+        <v>90</v>
+      </c>
+      <c r="F181" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A182" s="11">
+        <v>532</v>
+      </c>
+      <c r="B182" s="8">
+        <v>46241</v>
+      </c>
+      <c r="C182" s="6">
+        <v>0.44122685185185184</v>
+      </c>
+      <c r="D182" s="11">
+        <v>100</v>
+      </c>
+      <c r="F182" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G182" s="7">
+        <v>2.9</v>
+      </c>
+      <c r="H182" s="7">
+        <v>24.2</v>
+      </c>
+      <c r="I182" s="7">
+        <v>-9.4</v>
+      </c>
+      <c r="J182" s="7">
+        <v>20.5</v>
+      </c>
+      <c r="K182" s="4">
+        <v>2.8</v>
+      </c>
+      <c r="L182" s="4">
+        <v>24.4</v>
+      </c>
+      <c r="M182" s="4">
+        <v>-10.199999999999999</v>
+      </c>
+      <c r="N182" s="4">
+        <v>-17.5</v>
+      </c>
+    </row>
+    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A183" s="11">
+        <v>532</v>
+      </c>
+      <c r="B183" s="8">
+        <v>46241</v>
+      </c>
+      <c r="C183" s="6">
+        <v>0.44482638888888887</v>
+      </c>
+      <c r="D183" s="11">
+        <v>100</v>
+      </c>
+      <c r="F183" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A184" s="11">
+        <v>532</v>
+      </c>
+      <c r="B184" s="8">
+        <v>46241</v>
+      </c>
+      <c r="C184" s="6">
+        <v>0.4463078703703704</v>
+      </c>
+      <c r="D184" s="11">
+        <v>110</v>
+      </c>
+      <c r="F184" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G184" s="7">
+        <v>2.4</v>
+      </c>
+      <c r="H184" s="7">
+        <v>23.3</v>
+      </c>
+      <c r="I184" s="7">
+        <v>-10.4</v>
+      </c>
+      <c r="J184" s="7">
+        <v>29.9</v>
+      </c>
+      <c r="K184" s="4">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="L184" s="4">
+        <v>23.2</v>
+      </c>
+      <c r="M184" s="4">
+        <v>-11.2</v>
+      </c>
+      <c r="N184" s="4">
+        <v>-21</v>
+      </c>
+    </row>
+    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A185" s="11">
+        <v>532</v>
+      </c>
+      <c r="B185" s="8">
+        <v>46241</v>
+      </c>
+      <c r="C185" s="6">
+        <v>0.44883101851851853</v>
+      </c>
+      <c r="D185" s="11">
+        <v>110</v>
+      </c>
+      <c r="F185" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A186" s="11">
+        <v>532</v>
+      </c>
+      <c r="B186" s="8">
+        <v>46241</v>
+      </c>
+      <c r="C186" s="6">
+        <v>0.45055555555555554</v>
+      </c>
+      <c r="D186" s="11">
+        <v>120</v>
+      </c>
+      <c r="F186" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G186" s="7">
+        <v>2.6</v>
+      </c>
+      <c r="H186" s="7">
+        <v>23</v>
+      </c>
+      <c r="I186" s="7">
+        <v>-13.7</v>
+      </c>
+      <c r="J186" s="7">
+        <v>30.5</v>
+      </c>
+      <c r="K186" s="4">
+        <v>2.6</v>
+      </c>
+      <c r="L186" s="4">
+        <v>23</v>
+      </c>
+      <c r="M186" s="4">
+        <v>-12.6</v>
+      </c>
+      <c r="N186" s="4">
+        <v>-28.6</v>
+      </c>
+    </row>
+    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A187" s="11">
+        <v>532</v>
+      </c>
+      <c r="B187" s="8">
+        <v>46241</v>
+      </c>
+      <c r="C187" s="6">
+        <v>0.45196759259259262</v>
+      </c>
+      <c r="D187" s="11">
+        <v>120</v>
+      </c>
+      <c r="F187" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
